--- a/data/sars/pacific/tables/Pacific_2023_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_2023_Appendix2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555C8BB5-DA2A-D849-9C86-9CB3C56E03C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA65A0B3-26EC-3F4F-A7DD-C1845B27BB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5440" yWindow="580" windowWidth="28800" windowHeight="20180" xr2:uid="{11F333EC-CD41-C849-B489-265FED43AAE8}"/>
+    <workbookView xWindow="5440" yWindow="520" windowWidth="28800" windowHeight="20180" xr2:uid="{11F333EC-CD41-C849-B489-265FED43AAE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="131">
   <si>
     <t>n/a</t>
   </si>
@@ -92,9 +92,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>California sea lion (U.S.)</t>
   </si>
   <si>
@@ -423,6 +420,15 @@
   </si>
   <si>
     <t>≥1.6</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -821,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4122A673-9114-5A41-B113-FA6362814330}">
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74" bestFit="1" customWidth="1"/>
@@ -835,12 +841,12 @@
     <col min="9" max="9" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -879,12 +885,15 @@
         <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>257606</v>
@@ -905,10 +914,10 @@
         <v>14011</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>1</v>
@@ -926,9 +935,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>30968</v>
@@ -968,9 +977,9 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -1006,9 +1015,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -1044,9 +1053,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
@@ -1082,9 +1091,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
@@ -1120,9 +1129,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2">
         <v>187386</v>
@@ -1164,9 +1173,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2">
         <v>34187</v>
@@ -1204,9 +1213,9 @@
       </c>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2">
         <v>14050</v>
@@ -1248,9 +1257,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="5">
         <v>1564</v>
@@ -1289,10 +1298,13 @@
       <c r="N11" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="3">
         <v>4191</v>
@@ -1334,9 +1346,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2">
         <v>3760</v>
@@ -1357,10 +1369,10 @@
         <v>35</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>1</v>
@@ -1378,9 +1390,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>7777</v>
@@ -1401,10 +1413,10 @@
         <v>73</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>1</v>
@@ -1422,9 +1434,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5">
         <v>15303</v>
@@ -1465,10 +1477,13 @@
       <c r="N15" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6">
         <v>7492</v>
@@ -1509,10 +1524,13 @@
       <c r="N16" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="5">
         <v>22074</v>
@@ -1553,10 +1571,13 @@
       <c r="N17" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2">
         <v>11233</v>
@@ -1577,10 +1598,10 @@
         <v>66</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>1</v>
@@ -1598,9 +1619,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="3">
         <v>16498</v>
@@ -1621,10 +1642,10 @@
         <v>99</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>1</v>
@@ -1642,9 +1663,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3">
         <v>34999</v>
@@ -1686,9 +1707,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2">
         <v>6336</v>
@@ -1709,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>1</v>
@@ -1730,9 +1751,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="3">
         <v>453</v>
@@ -1753,10 +1774,10 @@
         <v>2.7</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>1</v>
@@ -1772,9 +1793,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2">
         <v>3477</v>
@@ -1795,10 +1816,10 @@
         <v>19.7</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>1</v>
@@ -1816,9 +1837,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="3">
         <v>29988</v>
@@ -1839,10 +1860,10 @@
         <v>225</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>1</v>
@@ -1860,9 +1881,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2">
         <v>1056308</v>
@@ -1883,10 +1904,10 @@
         <v>8889</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>1</v>
@@ -1904,9 +1925,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" s="3">
         <v>83379</v>
@@ -1927,10 +1948,10 @@
         <v>668</v>
       </c>
       <c r="H26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>1</v>
@@ -1948,9 +1969,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="3">
         <v>29285</v>
@@ -1971,10 +1992,10 @@
         <v>163</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>1</v>
@@ -1992,9 +2013,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" s="3">
         <v>300</v>
@@ -2036,9 +2057,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="6">
         <v>73</v>
@@ -2079,10 +2100,13 @@
       <c r="N29" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" s="3">
         <v>836</v>
@@ -2124,9 +2148,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2">
         <v>1363</v>
@@ -2147,7 +2171,7 @@
         <v>8.9</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>2</v>
@@ -2168,9 +2192,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" s="2">
         <v>3044</v>
@@ -2212,9 +2236,9 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2">
         <v>5454</v>
@@ -2256,9 +2280,9 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" s="2">
         <v>4111</v>
@@ -2300,9 +2324,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>2</v>
@@ -2344,9 +2368,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="5">
         <v>2606</v>
@@ -2387,10 +2411,13 @@
       <c r="N36" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O36" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="3">
         <v>29960</v>
@@ -2432,9 +2459,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="3">
         <v>290</v>
@@ -2476,9 +2503,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="3">
         <v>1496</v>
@@ -2518,9 +2545,9 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="2">
         <v>3477</v>
@@ -2562,9 +2589,9 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="6">
         <v>1898</v>
@@ -2585,10 +2612,10 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H41" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>4</v>
@@ -2605,10 +2632,13 @@
       <c r="N41" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="5">
         <v>11065</v>
@@ -2629,10 +2659,10 @@
         <v>80</v>
       </c>
       <c r="H42" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>4</v>
@@ -2649,10 +2679,13 @@
       <c r="N42" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O42" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="6">
         <v>864</v>
@@ -2693,10 +2726,13 @@
       <c r="N43" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O43" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44" s="6">
         <v>915</v>
@@ -2717,10 +2753,10 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H44" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I44" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>1</v>
@@ -2737,10 +2773,13 @@
       <c r="N44" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>2</v>
@@ -2782,9 +2821,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46" s="6">
         <v>83915</v>
@@ -2825,10 +2864,13 @@
       <c r="N46" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O46" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>2</v>
@@ -2870,9 +2912,9 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B48" s="6">
         <v>6979</v>
@@ -2913,10 +2955,13 @@
       <c r="N48" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O48" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" s="6">
         <v>24669</v>
@@ -2957,10 +3002,13 @@
       <c r="N49" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B50" s="6">
         <v>112</v>
@@ -3001,10 +3049,13 @@
       <c r="N50" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" s="6">
         <v>112</v>
@@ -3045,10 +3096,13 @@
       <c r="N51" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O51" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B52" s="6">
         <v>64</v>
@@ -3089,10 +3143,13 @@
       <c r="N52" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B53" s="6">
         <v>136</v>
@@ -3113,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>2</v>
@@ -3133,10 +3190,13 @@
       <c r="N53" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54" s="5">
         <v>67313</v>
@@ -3177,10 +3237,13 @@
       <c r="N54" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O54" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
@@ -3217,10 +3280,13 @@
       <c r="N55" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O55" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
@@ -3257,10 +3323,13 @@
       <c r="N56" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O56" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
@@ -3297,10 +3366,13 @@
       <c r="N57" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O57" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" s="3">
         <v>665</v>
@@ -3321,7 +3393,7 @@
         <v>6.2</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>2</v>
@@ -3342,9 +3414,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>0</v>
@@ -3365,7 +3437,7 @@
         <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>2</v>
@@ -3384,9 +3456,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>0</v>
@@ -3424,9 +3496,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>2</v>
@@ -3466,9 +3538,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>2</v>
@@ -3506,9 +3578,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>2</v>
@@ -3546,9 +3618,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>2</v>
@@ -3586,9 +3658,9 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B65" s="5">
         <v>64343</v>
@@ -3629,10 +3701,13 @@
       <c r="N65" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O65" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3">
         <v>40960</v>
@@ -3674,9 +3749,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B67" s="2">
         <v>40647</v>
@@ -3718,9 +3793,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>2</v>
@@ -3756,9 +3831,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B69" s="2">
         <v>10328</v>
@@ -3800,9 +3875,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B70" s="6">
         <v>477</v>
@@ -3843,10 +3918,13 @@
       <c r="N70" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O70" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B71" s="5">
         <v>5528</v>
@@ -3887,10 +3965,13 @@
       <c r="N71" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O71" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B72" s="6">
         <v>167</v>
@@ -3931,10 +4012,13 @@
       <c r="N72" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O72" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B73" s="3">
         <v>1329</v>
@@ -3972,9 +4056,9 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>2</v>
@@ -4012,9 +4096,9 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B75" s="3">
         <v>161</v>
@@ -4056,9 +4140,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B76" s="6">
         <v>19242</v>
@@ -4099,10 +4183,13 @@
       <c r="N76" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O76" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B77" s="2">
         <v>1132</v>
@@ -4144,9 +4231,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B78" s="2">
         <v>2550</v>
@@ -4188,9 +4275,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B79" s="2">
         <v>4431</v>
@@ -4232,9 +4319,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B80" s="2">
         <v>42083</v>
@@ -4276,9 +4363,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>2</v>
@@ -4320,9 +4407,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B82" s="2">
         <v>5707</v>
@@ -4364,9 +4451,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B83" s="3">
         <v>133</v>
@@ -4406,9 +4493,9 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B84" s="3">
         <v>203</v>
@@ -4450,9 +4537,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B85" s="6">
         <v>791</v>
@@ -4493,10 +4580,13 @@
       <c r="N85" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O85" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B86" s="3">
         <v>391</v>
@@ -4538,9 +4628,9 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B87" s="3">
         <v>438</v>
@@ -4582,9 +4672,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>2</v>
@@ -4622,7 +4712,9 @@
       <c r="M88" s="3">
         <v>2008</v>
       </c>
-      <c r="N88" s="3"/>
+      <c r="N88" s="3">
+        <v>2009</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/sars/pacific/tables/Pacific_2023_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_2023_Appendix2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
